--- a/data/Employe.xlsx
+++ b/data/Employe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Yadhu Projects\Chatbot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC4243E-58D4-4ED2-9E70-7BD048ABB9A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426E1CE1-787E-430D-BDD4-EDEC1DF29552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{237E2F31-7E00-4E11-A7A5-511FF5DF51D1}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="510">
   <si>
     <t>SL</t>
   </si>
@@ -1563,6 +1564,9 @@
   </si>
   <si>
     <t>Him Self</t>
+  </si>
+  <si>
+    <t>Salary Confidential</t>
   </si>
 </sst>
 </file>
@@ -1679,10 +1683,10 @@
     <tableColumn id="3" xr3:uid="{8F3E8A5F-05CC-486C-BA3B-092814A4B032}" name="Name" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{9F181852-E985-4864-9022-730DDA73A9EE}" name="Email" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{5BFDC752-C8AB-4B1F-B218-E0A7482B5511}" name="Base Salary" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{C18E7B6E-C4CE-4D4D-A1DF-817368D5B38A}" name="TakeLeave" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{7D15E95B-CD96-485A-8248-C0228B4AC192}" name="AvailableLeave" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{4EC8A7EA-B38B-4695-A598-07DF6D499328}" name="Under" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{E18DF15A-25C4-4B0E-A8FA-7C943167256F}" name="Designation" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{C18E7B6E-C4CE-4D4D-A1DF-817368D5B38A}" name="TakeLeave" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{7D15E95B-CD96-485A-8248-C0228B4AC192}" name="AvailableLeave" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{4EC8A7EA-B38B-4695-A598-07DF6D499328}" name="Under" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{E18DF15A-25C4-4B0E-A8FA-7C943167256F}" name="Designation" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2060,8 +2064,8 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1">
-        <v>12000</v>
+      <c r="E2" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -2089,8 +2093,8 @@
       <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1">
-        <v>12000</v>
+      <c r="E3" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F3" s="1">
         <v>5</v>
@@ -2118,8 +2122,8 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1">
-        <v>12000</v>
+      <c r="E4" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -2147,8 +2151,8 @@
       <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1">
-        <v>12000</v>
+      <c r="E5" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F5" s="1">
         <v>5</v>
@@ -2176,8 +2180,8 @@
       <c r="D6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="1">
-        <v>12000</v>
+      <c r="E6" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
@@ -2205,8 +2209,8 @@
       <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1">
-        <v>12000</v>
+      <c r="E7" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
@@ -2234,8 +2238,8 @@
       <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="1">
-        <v>12000</v>
+      <c r="E8" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
@@ -2263,8 +2267,8 @@
       <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="1">
-        <v>12000</v>
+      <c r="E9" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F9" s="1">
         <v>5</v>
@@ -2292,8 +2296,8 @@
       <c r="D10" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="1">
-        <v>12000</v>
+      <c r="E10" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
@@ -2321,8 +2325,8 @@
       <c r="D11" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="1">
-        <v>12000</v>
+      <c r="E11" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F11" s="1">
         <v>5</v>
@@ -2350,8 +2354,8 @@
       <c r="D12" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="1">
-        <v>12000</v>
+      <c r="E12" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F12" s="1">
         <v>5</v>
@@ -2379,8 +2383,8 @@
       <c r="D13" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="1">
-        <v>12000</v>
+      <c r="E13" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F13" s="1">
         <v>5</v>
@@ -2408,8 +2412,8 @@
       <c r="D14" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="1">
-        <v>12000</v>
+      <c r="E14" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F14" s="1">
         <v>5</v>
@@ -2437,8 +2441,8 @@
       <c r="D15" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="1">
-        <v>12000</v>
+      <c r="E15" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -2466,8 +2470,8 @@
       <c r="D16" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="1">
-        <v>12000</v>
+      <c r="E16" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F16" s="1">
         <v>5</v>
@@ -2495,8 +2499,8 @@
       <c r="D17" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="1">
-        <v>12000</v>
+      <c r="E17" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F17" s="1">
         <v>5</v>
@@ -2524,8 +2528,8 @@
       <c r="D18" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="1">
-        <v>12000</v>
+      <c r="E18" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F18" s="1">
         <v>5</v>
@@ -2553,8 +2557,8 @@
       <c r="D19" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="1">
-        <v>12000</v>
+      <c r="E19" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F19" s="1">
         <v>5</v>
@@ -2582,8 +2586,8 @@
       <c r="D20" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="1">
-        <v>12000</v>
+      <c r="E20" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F20" s="1">
         <v>5</v>
@@ -2611,8 +2615,8 @@
       <c r="D21" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="1">
-        <v>12000</v>
+      <c r="E21" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F21" s="1">
         <v>5</v>
@@ -2640,8 +2644,8 @@
       <c r="D22" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="1">
-        <v>12000</v>
+      <c r="E22" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
@@ -2669,8 +2673,8 @@
       <c r="D23" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="1">
-        <v>12000</v>
+      <c r="E23" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F23" s="1">
         <v>5</v>
@@ -2698,8 +2702,8 @@
       <c r="D24" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="1">
-        <v>12000</v>
+      <c r="E24" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F24" s="1">
         <v>5</v>
@@ -2727,8 +2731,8 @@
       <c r="D25" t="s">
         <v>82</v>
       </c>
-      <c r="E25" s="1">
-        <v>12000</v>
+      <c r="E25" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F25" s="1">
         <v>5</v>
@@ -2756,8 +2760,8 @@
       <c r="D26" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="1">
-        <v>12000</v>
+      <c r="E26" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F26" s="1">
         <v>5</v>
@@ -2785,8 +2789,8 @@
       <c r="D27" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="1">
-        <v>12000</v>
+      <c r="E27" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F27" s="1">
         <v>5</v>
@@ -2814,8 +2818,8 @@
       <c r="D28" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="1">
-        <v>12000</v>
+      <c r="E28" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F28" s="1">
         <v>5</v>
@@ -2843,8 +2847,8 @@
       <c r="D29" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="1">
-        <v>12000</v>
+      <c r="E29" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F29" s="1">
         <v>5</v>
@@ -2872,8 +2876,8 @@
       <c r="D30" t="s">
         <v>97</v>
       </c>
-      <c r="E30" s="1">
-        <v>12000</v>
+      <c r="E30" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F30" s="1">
         <v>5</v>
@@ -2901,8 +2905,8 @@
       <c r="D31" t="s">
         <v>100</v>
       </c>
-      <c r="E31" s="1">
-        <v>12000</v>
+      <c r="E31" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F31" s="1">
         <v>5</v>
@@ -2930,8 +2934,8 @@
       <c r="D32" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="1">
-        <v>12000</v>
+      <c r="E32" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F32" s="1">
         <v>5</v>
@@ -2959,8 +2963,8 @@
       <c r="D33" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="1">
-        <v>12000</v>
+      <c r="E33" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F33" s="1">
         <v>5</v>
@@ -2988,8 +2992,8 @@
       <c r="D34" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="1">
-        <v>12000</v>
+      <c r="E34" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F34" s="1">
         <v>5</v>
@@ -3017,8 +3021,8 @@
       <c r="D35" t="s">
         <v>112</v>
       </c>
-      <c r="E35" s="1">
-        <v>12000</v>
+      <c r="E35" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F35" s="1">
         <v>5</v>
@@ -3046,8 +3050,8 @@
       <c r="D36" t="s">
         <v>115</v>
       </c>
-      <c r="E36" s="1">
-        <v>12000</v>
+      <c r="E36" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F36" s="1">
         <v>5</v>
@@ -3075,8 +3079,8 @@
       <c r="D37" t="s">
         <v>118</v>
       </c>
-      <c r="E37" s="1">
-        <v>12000</v>
+      <c r="E37" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F37" s="1">
         <v>5</v>
@@ -3104,8 +3108,8 @@
       <c r="D38" t="s">
         <v>121</v>
       </c>
-      <c r="E38" s="1">
-        <v>12000</v>
+      <c r="E38" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F38" s="1">
         <v>5</v>
@@ -3133,8 +3137,8 @@
       <c r="D39" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="1">
-        <v>12000</v>
+      <c r="E39" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F39" s="1">
         <v>5</v>
@@ -3162,8 +3166,8 @@
       <c r="D40" t="s">
         <v>127</v>
       </c>
-      <c r="E40" s="1">
-        <v>12000</v>
+      <c r="E40" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
@@ -3191,8 +3195,8 @@
       <c r="D41" t="s">
         <v>130</v>
       </c>
-      <c r="E41" s="1">
-        <v>12000</v>
+      <c r="E41" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F41" s="1">
         <v>5</v>
@@ -3220,8 +3224,8 @@
       <c r="D42" t="s">
         <v>133</v>
       </c>
-      <c r="E42" s="1">
-        <v>12000</v>
+      <c r="E42" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F42" s="1">
         <v>5</v>
@@ -3249,8 +3253,8 @@
       <c r="D43" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="1">
-        <v>12000</v>
+      <c r="E43" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F43" s="1">
         <v>5</v>
@@ -3278,8 +3282,8 @@
       <c r="D44" t="s">
         <v>139</v>
       </c>
-      <c r="E44" s="1">
-        <v>12000</v>
+      <c r="E44" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F44" s="1">
         <v>5</v>
@@ -3307,8 +3311,8 @@
       <c r="D45" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="1">
-        <v>12000</v>
+      <c r="E45" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F45" s="1">
         <v>5</v>
@@ -3336,8 +3340,8 @@
       <c r="D46" t="s">
         <v>145</v>
       </c>
-      <c r="E46" s="1">
-        <v>12000</v>
+      <c r="E46" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F46" s="1">
         <v>5</v>
@@ -3365,8 +3369,8 @@
       <c r="D47" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="1">
-        <v>12000</v>
+      <c r="E47" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F47" s="1">
         <v>5</v>
@@ -3394,8 +3398,8 @@
       <c r="D48" t="s">
         <v>151</v>
       </c>
-      <c r="E48" s="1">
-        <v>12000</v>
+      <c r="E48" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F48" s="1">
         <v>5</v>
@@ -3423,8 +3427,8 @@
       <c r="D49" t="s">
         <v>154</v>
       </c>
-      <c r="E49" s="1">
-        <v>12000</v>
+      <c r="E49" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F49" s="1">
         <v>5</v>
@@ -3452,8 +3456,8 @@
       <c r="D50" t="s">
         <v>157</v>
       </c>
-      <c r="E50" s="1">
-        <v>12000</v>
+      <c r="E50" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F50" s="1">
         <v>5</v>
@@ -3481,8 +3485,8 @@
       <c r="D51" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="1">
-        <v>12000</v>
+      <c r="E51" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F51" s="1">
         <v>5</v>
@@ -3510,8 +3514,8 @@
       <c r="D52" t="s">
         <v>163</v>
       </c>
-      <c r="E52" s="1">
-        <v>12000</v>
+      <c r="E52" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F52" s="1">
         <v>5</v>
@@ -3539,8 +3543,8 @@
       <c r="D53" t="s">
         <v>166</v>
       </c>
-      <c r="E53" s="1">
-        <v>12000</v>
+      <c r="E53" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F53" s="1">
         <v>5</v>
@@ -3568,8 +3572,8 @@
       <c r="D54" t="s">
         <v>169</v>
       </c>
-      <c r="E54" s="1">
-        <v>12000</v>
+      <c r="E54" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F54" s="1">
         <v>5</v>
@@ -3597,8 +3601,8 @@
       <c r="D55" t="s">
         <v>172</v>
       </c>
-      <c r="E55" s="1">
-        <v>12000</v>
+      <c r="E55" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F55" s="1">
         <v>5</v>
@@ -3626,8 +3630,8 @@
       <c r="D56" t="s">
         <v>175</v>
       </c>
-      <c r="E56" s="1">
-        <v>12000</v>
+      <c r="E56" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F56" s="1">
         <v>5</v>
@@ -3655,8 +3659,8 @@
       <c r="D57" t="s">
         <v>178</v>
       </c>
-      <c r="E57" s="1">
-        <v>12000</v>
+      <c r="E57" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F57" s="1">
         <v>5</v>
@@ -3684,8 +3688,8 @@
       <c r="D58" t="s">
         <v>181</v>
       </c>
-      <c r="E58" s="1">
-        <v>12000</v>
+      <c r="E58" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F58" s="1">
         <v>5</v>
@@ -3713,8 +3717,8 @@
       <c r="D59" t="s">
         <v>184</v>
       </c>
-      <c r="E59" s="1">
-        <v>12000</v>
+      <c r="E59" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F59" s="1">
         <v>5</v>
@@ -3742,8 +3746,8 @@
       <c r="D60" t="s">
         <v>187</v>
       </c>
-      <c r="E60" s="1">
-        <v>12000</v>
+      <c r="E60" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F60" s="1">
         <v>5</v>
@@ -3771,8 +3775,8 @@
       <c r="D61" t="s">
         <v>190</v>
       </c>
-      <c r="E61" s="1">
-        <v>12000</v>
+      <c r="E61" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F61" s="1">
         <v>5</v>
@@ -3800,8 +3804,8 @@
       <c r="D62" t="s">
         <v>193</v>
       </c>
-      <c r="E62" s="1">
-        <v>12000</v>
+      <c r="E62" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F62" s="1">
         <v>5</v>
@@ -3829,8 +3833,8 @@
       <c r="D63" t="s">
         <v>196</v>
       </c>
-      <c r="E63" s="1">
-        <v>12000</v>
+      <c r="E63" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F63" s="1">
         <v>5</v>
@@ -3858,8 +3862,8 @@
       <c r="D64" t="s">
         <v>199</v>
       </c>
-      <c r="E64" s="1">
-        <v>12000</v>
+      <c r="E64" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F64" s="1">
         <v>5</v>
@@ -3887,8 +3891,8 @@
       <c r="D65" t="s">
         <v>202</v>
       </c>
-      <c r="E65" s="1">
-        <v>12000</v>
+      <c r="E65" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F65" s="1">
         <v>5</v>
@@ -3916,8 +3920,8 @@
       <c r="D66" t="s">
         <v>205</v>
       </c>
-      <c r="E66" s="1">
-        <v>12000</v>
+      <c r="E66" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F66" s="1">
         <v>5</v>
@@ -3945,8 +3949,8 @@
       <c r="D67" t="s">
         <v>208</v>
       </c>
-      <c r="E67" s="1">
-        <v>12000</v>
+      <c r="E67" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F67" s="1">
         <v>5</v>
@@ -3974,8 +3978,8 @@
       <c r="D68" t="s">
         <v>211</v>
       </c>
-      <c r="E68" s="1">
-        <v>12000</v>
+      <c r="E68" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F68" s="1">
         <v>5</v>
@@ -4003,8 +4007,8 @@
       <c r="D69" t="s">
         <v>214</v>
       </c>
-      <c r="E69" s="1">
-        <v>12000</v>
+      <c r="E69" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F69" s="1">
         <v>5</v>
@@ -4032,8 +4036,8 @@
       <c r="D70" t="s">
         <v>217</v>
       </c>
-      <c r="E70" s="1">
-        <v>12000</v>
+      <c r="E70" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F70" s="1">
         <v>5</v>
@@ -4061,8 +4065,8 @@
       <c r="D71" t="s">
         <v>220</v>
       </c>
-      <c r="E71" s="1">
-        <v>12000</v>
+      <c r="E71" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F71" s="1">
         <v>5</v>
@@ -4090,8 +4094,8 @@
       <c r="D72" t="s">
         <v>223</v>
       </c>
-      <c r="E72" s="1">
-        <v>12000</v>
+      <c r="E72" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F72" s="1">
         <v>5</v>
@@ -4119,8 +4123,8 @@
       <c r="D73" t="s">
         <v>226</v>
       </c>
-      <c r="E73" s="1">
-        <v>12000</v>
+      <c r="E73" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F73" s="1">
         <v>5</v>
@@ -4148,8 +4152,8 @@
       <c r="D74" t="s">
         <v>229</v>
       </c>
-      <c r="E74" s="1">
-        <v>12000</v>
+      <c r="E74" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F74" s="1">
         <v>5</v>
@@ -4177,8 +4181,8 @@
       <c r="D75" t="s">
         <v>232</v>
       </c>
-      <c r="E75" s="1">
-        <v>12000</v>
+      <c r="E75" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F75" s="1">
         <v>5</v>
@@ -4206,8 +4210,8 @@
       <c r="D76" t="s">
         <v>235</v>
       </c>
-      <c r="E76" s="1">
-        <v>12000</v>
+      <c r="E76" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F76" s="1">
         <v>5</v>
@@ -4235,8 +4239,8 @@
       <c r="D77" t="s">
         <v>238</v>
       </c>
-      <c r="E77" s="1">
-        <v>12000</v>
+      <c r="E77" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F77" s="1">
         <v>5</v>
@@ -4264,8 +4268,8 @@
       <c r="D78" t="s">
         <v>241</v>
       </c>
-      <c r="E78" s="1">
-        <v>12000</v>
+      <c r="E78" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F78" s="1">
         <v>5</v>
@@ -4293,8 +4297,8 @@
       <c r="D79" t="s">
         <v>244</v>
       </c>
-      <c r="E79" s="1">
-        <v>12000</v>
+      <c r="E79" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F79" s="1">
         <v>5</v>
@@ -4322,8 +4326,8 @@
       <c r="D80" t="s">
         <v>247</v>
       </c>
-      <c r="E80" s="1">
-        <v>12000</v>
+      <c r="E80" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F80" s="1">
         <v>5</v>
@@ -4351,8 +4355,8 @@
       <c r="D81" t="s">
         <v>250</v>
       </c>
-      <c r="E81" s="1">
-        <v>12000</v>
+      <c r="E81" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F81" s="1">
         <v>5</v>
@@ -4380,8 +4384,8 @@
       <c r="D82" t="s">
         <v>253</v>
       </c>
-      <c r="E82" s="1">
-        <v>12000</v>
+      <c r="E82" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F82" s="1">
         <v>5</v>
@@ -4409,8 +4413,8 @@
       <c r="D83" t="s">
         <v>256</v>
       </c>
-      <c r="E83" s="1">
-        <v>12000</v>
+      <c r="E83" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F83" s="1">
         <v>5</v>
@@ -4438,8 +4442,8 @@
       <c r="D84" t="s">
         <v>259</v>
       </c>
-      <c r="E84" s="1">
-        <v>0</v>
+      <c r="E84" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F84" s="1">
         <v>5</v>
@@ -4467,8 +4471,8 @@
       <c r="D85" t="s">
         <v>262</v>
       </c>
-      <c r="E85" s="1">
-        <v>12000</v>
+      <c r="E85" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F85" s="1">
         <v>5</v>
@@ -4496,8 +4500,8 @@
       <c r="D86" t="s">
         <v>265</v>
       </c>
-      <c r="E86" s="1">
-        <v>12000</v>
+      <c r="E86" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F86" s="1">
         <v>5</v>
@@ -4525,8 +4529,8 @@
       <c r="D87" t="s">
         <v>268</v>
       </c>
-      <c r="E87" s="1">
-        <v>12000</v>
+      <c r="E87" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F87" s="1">
         <v>5</v>
@@ -4554,8 +4558,8 @@
       <c r="D88" t="s">
         <v>271</v>
       </c>
-      <c r="E88" s="1">
-        <v>12000</v>
+      <c r="E88" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F88" s="1">
         <v>5</v>
@@ -4583,8 +4587,8 @@
       <c r="D89" t="s">
         <v>274</v>
       </c>
-      <c r="E89" s="1">
-        <v>12000</v>
+      <c r="E89" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F89" s="1">
         <v>5</v>
@@ -4612,8 +4616,8 @@
       <c r="D90" t="s">
         <v>277</v>
       </c>
-      <c r="E90" s="1">
-        <v>12000</v>
+      <c r="E90" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F90" s="1">
         <v>5</v>
@@ -4641,8 +4645,8 @@
       <c r="D91" t="s">
         <v>280</v>
       </c>
-      <c r="E91" s="1">
-        <v>12000</v>
+      <c r="E91" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F91" s="1">
         <v>5</v>
@@ -4670,8 +4674,8 @@
       <c r="D92" t="s">
         <v>283</v>
       </c>
-      <c r="E92" s="1">
-        <v>12000</v>
+      <c r="E92" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F92" s="1">
         <v>5</v>
@@ -4699,8 +4703,8 @@
       <c r="D93" t="s">
         <v>286</v>
       </c>
-      <c r="E93" s="1">
-        <v>12000</v>
+      <c r="E93" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F93" s="1">
         <v>5</v>
@@ -4728,8 +4732,8 @@
       <c r="D94" t="s">
         <v>289</v>
       </c>
-      <c r="E94" s="1">
-        <v>12000</v>
+      <c r="E94" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F94" s="1">
         <v>5</v>
@@ -4757,8 +4761,8 @@
       <c r="D95" t="s">
         <v>292</v>
       </c>
-      <c r="E95" s="1">
-        <v>12000</v>
+      <c r="E95" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F95" s="1">
         <v>5</v>
@@ -4786,8 +4790,8 @@
       <c r="D96" t="s">
         <v>295</v>
       </c>
-      <c r="E96" s="1">
-        <v>12000</v>
+      <c r="E96" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F96" s="1">
         <v>5</v>
@@ -4815,8 +4819,8 @@
       <c r="D97" t="s">
         <v>298</v>
       </c>
-      <c r="E97" s="1">
-        <v>12000</v>
+      <c r="E97" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F97" s="1">
         <v>5</v>
@@ -4844,8 +4848,8 @@
       <c r="D98" t="s">
         <v>301</v>
       </c>
-      <c r="E98" s="1">
-        <v>12000</v>
+      <c r="E98" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F98" s="1">
         <v>5</v>
@@ -4873,8 +4877,8 @@
       <c r="D99" t="s">
         <v>304</v>
       </c>
-      <c r="E99" s="1">
-        <v>12000</v>
+      <c r="E99" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F99" s="1">
         <v>5</v>
@@ -4902,8 +4906,8 @@
       <c r="D100" t="s">
         <v>307</v>
       </c>
-      <c r="E100" s="1">
-        <v>12000</v>
+      <c r="E100" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F100" s="1">
         <v>5</v>
@@ -4931,8 +4935,8 @@
       <c r="D101" t="s">
         <v>310</v>
       </c>
-      <c r="E101" s="1">
-        <v>12000</v>
+      <c r="E101" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F101" s="1">
         <v>5</v>
@@ -4960,8 +4964,8 @@
       <c r="D102" t="s">
         <v>313</v>
       </c>
-      <c r="E102" s="1">
-        <v>12000</v>
+      <c r="E102" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F102" s="1">
         <v>5</v>
@@ -4989,8 +4993,8 @@
       <c r="D103" t="s">
         <v>316</v>
       </c>
-      <c r="E103" s="1">
-        <v>12000</v>
+      <c r="E103" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F103" s="1">
         <v>5</v>
@@ -5018,8 +5022,8 @@
       <c r="D104" t="s">
         <v>319</v>
       </c>
-      <c r="E104" s="1">
-        <v>12000</v>
+      <c r="E104" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F104" s="1">
         <v>5</v>
@@ -5047,8 +5051,8 @@
       <c r="D105" t="s">
         <v>322</v>
       </c>
-      <c r="E105" s="1">
-        <v>12000</v>
+      <c r="E105" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F105" s="1">
         <v>5</v>
@@ -5076,8 +5080,8 @@
       <c r="D106" t="s">
         <v>325</v>
       </c>
-      <c r="E106" s="1">
-        <v>12000</v>
+      <c r="E106" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F106" s="1">
         <v>5</v>
@@ -5105,8 +5109,8 @@
       <c r="D107" t="s">
         <v>328</v>
       </c>
-      <c r="E107" s="1">
-        <v>12000</v>
+      <c r="E107" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F107" s="1">
         <v>5</v>
@@ -5134,8 +5138,8 @@
       <c r="D108" t="s">
         <v>331</v>
       </c>
-      <c r="E108" s="1">
-        <v>12000</v>
+      <c r="E108" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F108" s="1">
         <v>5</v>
@@ -5163,8 +5167,8 @@
       <c r="D109" t="s">
         <v>334</v>
       </c>
-      <c r="E109" s="1">
-        <v>12000</v>
+      <c r="E109" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F109" s="1">
         <v>5</v>
@@ -5192,8 +5196,8 @@
       <c r="D110" t="s">
         <v>337</v>
       </c>
-      <c r="E110" s="1">
-        <v>12000</v>
+      <c r="E110" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F110" s="1">
         <v>5</v>
@@ -5221,8 +5225,8 @@
       <c r="D111" t="s">
         <v>340</v>
       </c>
-      <c r="E111" s="1">
-        <v>12000</v>
+      <c r="E111" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F111" s="1">
         <v>5</v>
@@ -5250,8 +5254,8 @@
       <c r="D112" t="s">
         <v>343</v>
       </c>
-      <c r="E112" s="1">
-        <v>12000</v>
+      <c r="E112" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F112" s="1">
         <v>5</v>
@@ -5279,8 +5283,8 @@
       <c r="D113" t="s">
         <v>346</v>
       </c>
-      <c r="E113" s="1">
-        <v>12000</v>
+      <c r="E113" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F113" s="1">
         <v>5</v>
@@ -5308,8 +5312,8 @@
       <c r="D114" t="s">
         <v>349</v>
       </c>
-      <c r="E114" s="1">
-        <v>12000</v>
+      <c r="E114" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F114" s="1">
         <v>5</v>
@@ -5337,8 +5341,8 @@
       <c r="D115" t="s">
         <v>352</v>
       </c>
-      <c r="E115" s="1">
-        <v>12000</v>
+      <c r="E115" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F115" s="1">
         <v>5</v>
@@ -5366,8 +5370,8 @@
       <c r="D116" t="s">
         <v>355</v>
       </c>
-      <c r="E116" s="1">
-        <v>12000</v>
+      <c r="E116" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F116" s="1">
         <v>5</v>
@@ -5395,8 +5399,8 @@
       <c r="D117" t="s">
         <v>358</v>
       </c>
-      <c r="E117" s="1">
-        <v>12000</v>
+      <c r="E117" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F117" s="1">
         <v>5</v>
@@ -5424,8 +5428,8 @@
       <c r="D118" t="s">
         <v>361</v>
       </c>
-      <c r="E118" s="1">
-        <v>12000</v>
+      <c r="E118" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F118" s="1">
         <v>5</v>
@@ -5453,8 +5457,8 @@
       <c r="D119" t="s">
         <v>364</v>
       </c>
-      <c r="E119" s="1">
-        <v>12000</v>
+      <c r="E119" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F119" s="1">
         <v>5</v>
@@ -5482,8 +5486,8 @@
       <c r="D120" t="s">
         <v>367</v>
       </c>
-      <c r="E120" s="1">
-        <v>12000</v>
+      <c r="E120" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F120" s="1">
         <v>5</v>
@@ -5511,8 +5515,8 @@
       <c r="D121" t="s">
         <v>370</v>
       </c>
-      <c r="E121" s="1">
-        <v>12000</v>
+      <c r="E121" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F121" s="1">
         <v>5</v>
@@ -5540,8 +5544,8 @@
       <c r="D122" t="s">
         <v>373</v>
       </c>
-      <c r="E122" s="1">
-        <v>12000</v>
+      <c r="E122" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F122" s="1">
         <v>5</v>
@@ -5569,8 +5573,8 @@
       <c r="D123" t="s">
         <v>376</v>
       </c>
-      <c r="E123" s="1">
-        <v>12000</v>
+      <c r="E123" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F123" s="1">
         <v>5</v>
@@ -5598,8 +5602,8 @@
       <c r="D124" t="s">
         <v>379</v>
       </c>
-      <c r="E124" s="1">
-        <v>12000</v>
+      <c r="E124" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F124" s="1">
         <v>5</v>
@@ -5627,8 +5631,8 @@
       <c r="D125" t="s">
         <v>382</v>
       </c>
-      <c r="E125" s="1">
-        <v>12000</v>
+      <c r="E125" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F125" s="1">
         <v>5</v>
@@ -5656,8 +5660,8 @@
       <c r="D126" t="s">
         <v>385</v>
       </c>
-      <c r="E126" s="1">
-        <v>12000</v>
+      <c r="E126" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F126" s="1">
         <v>5</v>
@@ -5685,8 +5689,8 @@
       <c r="D127" t="s">
         <v>388</v>
       </c>
-      <c r="E127" s="1">
-        <v>12000</v>
+      <c r="E127" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F127" s="1">
         <v>5</v>
@@ -5714,8 +5718,8 @@
       <c r="D128" t="s">
         <v>391</v>
       </c>
-      <c r="E128" s="1">
-        <v>12000</v>
+      <c r="E128" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F128" s="1">
         <v>5</v>
@@ -5743,8 +5747,8 @@
       <c r="D129" t="s">
         <v>394</v>
       </c>
-      <c r="E129" s="1">
-        <v>12000</v>
+      <c r="E129" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F129" s="1">
         <v>5</v>
@@ -5772,8 +5776,8 @@
       <c r="D130" t="s">
         <v>397</v>
       </c>
-      <c r="E130" s="1">
-        <v>12000</v>
+      <c r="E130" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F130" s="1">
         <v>5</v>
@@ -5801,8 +5805,8 @@
       <c r="D131" t="s">
         <v>400</v>
       </c>
-      <c r="E131" s="1">
-        <v>12000</v>
+      <c r="E131" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F131" s="1">
         <v>5</v>
@@ -5830,8 +5834,8 @@
       <c r="D132" t="s">
         <v>403</v>
       </c>
-      <c r="E132" s="1">
-        <v>12000</v>
+      <c r="E132" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F132" s="1">
         <v>5</v>
@@ -5859,8 +5863,8 @@
       <c r="D133" t="s">
         <v>406</v>
       </c>
-      <c r="E133" s="1">
-        <v>12000</v>
+      <c r="E133" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F133" s="1">
         <v>5</v>
@@ -5888,8 +5892,8 @@
       <c r="D134" t="s">
         <v>409</v>
       </c>
-      <c r="E134" s="1">
-        <v>12000</v>
+      <c r="E134" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F134" s="1">
         <v>5</v>
@@ -5917,8 +5921,8 @@
       <c r="D135" t="s">
         <v>412</v>
       </c>
-      <c r="E135" s="1">
-        <v>12000</v>
+      <c r="E135" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F135" s="1">
         <v>5</v>
@@ -5946,8 +5950,8 @@
       <c r="D136" t="s">
         <v>415</v>
       </c>
-      <c r="E136" s="1">
-        <v>12000</v>
+      <c r="E136" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F136" s="1">
         <v>5</v>
@@ -5975,8 +5979,8 @@
       <c r="D137" t="s">
         <v>418</v>
       </c>
-      <c r="E137" s="1">
-        <v>12000</v>
+      <c r="E137" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F137" s="1">
         <v>5</v>
@@ -6004,8 +6008,8 @@
       <c r="D138" t="s">
         <v>421</v>
       </c>
-      <c r="E138" s="1">
-        <v>12000</v>
+      <c r="E138" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F138" s="1">
         <v>5</v>
@@ -6033,8 +6037,8 @@
       <c r="D139" t="s">
         <v>424</v>
       </c>
-      <c r="E139" s="1">
-        <v>12000</v>
+      <c r="E139" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F139" s="1">
         <v>5</v>
@@ -6062,8 +6066,8 @@
       <c r="D140" t="s">
         <v>427</v>
       </c>
-      <c r="E140" s="1">
-        <v>12000</v>
+      <c r="E140" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F140" s="1">
         <v>5</v>
@@ -6091,8 +6095,8 @@
       <c r="D141" t="s">
         <v>430</v>
       </c>
-      <c r="E141" s="1">
-        <v>12000</v>
+      <c r="E141" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F141" s="1">
         <v>5</v>
@@ -6120,8 +6124,8 @@
       <c r="D142" t="s">
         <v>433</v>
       </c>
-      <c r="E142" s="1">
-        <v>12000</v>
+      <c r="E142" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F142" s="1">
         <v>5</v>
@@ -6149,8 +6153,8 @@
       <c r="D143" t="s">
         <v>436</v>
       </c>
-      <c r="E143" s="1">
-        <v>12000</v>
+      <c r="E143" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F143" s="1">
         <v>5</v>
@@ -6178,8 +6182,8 @@
       <c r="D144" t="s">
         <v>439</v>
       </c>
-      <c r="E144" s="1">
-        <v>12000</v>
+      <c r="E144" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F144" s="1">
         <v>5</v>
@@ -6207,8 +6211,8 @@
       <c r="D145" t="s">
         <v>442</v>
       </c>
-      <c r="E145" s="1">
-        <v>12000</v>
+      <c r="E145" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F145" s="1">
         <v>5</v>
@@ -6236,8 +6240,8 @@
       <c r="D146" t="s">
         <v>445</v>
       </c>
-      <c r="E146" s="1">
-        <v>12000</v>
+      <c r="E146" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F146" s="1">
         <v>5</v>
@@ -6265,8 +6269,8 @@
       <c r="D147" t="s">
         <v>448</v>
       </c>
-      <c r="E147" s="1">
-        <v>12000</v>
+      <c r="E147" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F147" s="1">
         <v>5</v>
@@ -6294,8 +6298,8 @@
       <c r="D148" t="s">
         <v>451</v>
       </c>
-      <c r="E148" s="1">
-        <v>12000</v>
+      <c r="E148" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F148" s="1">
         <v>5</v>
@@ -6323,8 +6327,8 @@
       <c r="D149" t="s">
         <v>454</v>
       </c>
-      <c r="E149" s="1">
-        <v>12000</v>
+      <c r="E149" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F149" s="1">
         <v>5</v>
@@ -6352,8 +6356,8 @@
       <c r="D150" t="s">
         <v>457</v>
       </c>
-      <c r="E150" s="1">
-        <v>12000</v>
+      <c r="E150" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F150" s="1">
         <v>5</v>
@@ -6381,8 +6385,8 @@
       <c r="D151" t="s">
         <v>460</v>
       </c>
-      <c r="E151" s="1">
-        <v>12000</v>
+      <c r="E151" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F151" s="1">
         <v>5</v>
@@ -6410,8 +6414,8 @@
       <c r="D152" t="s">
         <v>463</v>
       </c>
-      <c r="E152" s="1">
-        <v>12000</v>
+      <c r="E152" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F152" s="1">
         <v>5</v>
@@ -6439,8 +6443,8 @@
       <c r="D153" t="s">
         <v>466</v>
       </c>
-      <c r="E153" s="1">
-        <v>12000</v>
+      <c r="E153" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F153" s="1">
         <v>5</v>
@@ -6468,8 +6472,8 @@
       <c r="D154" t="s">
         <v>469</v>
       </c>
-      <c r="E154" s="1">
-        <v>12000</v>
+      <c r="E154" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F154" s="1">
         <v>5</v>
@@ -6497,8 +6501,8 @@
       <c r="D155" t="s">
         <v>472</v>
       </c>
-      <c r="E155" s="1">
-        <v>12000</v>
+      <c r="E155" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F155" s="1">
         <v>5</v>
@@ -6526,8 +6530,8 @@
       <c r="D156" t="s">
         <v>475</v>
       </c>
-      <c r="E156" s="1">
-        <v>12000</v>
+      <c r="E156" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F156" s="1">
         <v>5</v>
@@ -6555,8 +6559,8 @@
       <c r="D157" t="s">
         <v>478</v>
       </c>
-      <c r="E157" s="1">
-        <v>12000</v>
+      <c r="E157" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F157" s="1">
         <v>5</v>
@@ -6584,8 +6588,8 @@
       <c r="D158" t="s">
         <v>481</v>
       </c>
-      <c r="E158" s="1">
-        <v>12000</v>
+      <c r="E158" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F158" s="1">
         <v>5</v>
@@ -6613,8 +6617,8 @@
       <c r="D159" t="s">
         <v>484</v>
       </c>
-      <c r="E159" s="1">
-        <v>12000</v>
+      <c r="E159" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F159" s="1">
         <v>5</v>
@@ -6642,8 +6646,8 @@
       <c r="D160" t="s">
         <v>487</v>
       </c>
-      <c r="E160" s="1">
-        <v>12000</v>
+      <c r="E160" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F160" s="1">
         <v>5</v>
@@ -6671,8 +6675,8 @@
       <c r="D161" t="s">
         <v>490</v>
       </c>
-      <c r="E161" s="1">
-        <v>12000</v>
+      <c r="E161" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F161" s="1">
         <v>5</v>
@@ -6700,8 +6704,8 @@
       <c r="D162" t="s">
         <v>493</v>
       </c>
-      <c r="E162" s="1">
-        <v>12000</v>
+      <c r="E162" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F162" s="1">
         <v>5</v>
@@ -6729,8 +6733,8 @@
       <c r="D163" t="s">
         <v>496</v>
       </c>
-      <c r="E163" s="1">
-        <v>12000</v>
+      <c r="E163" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F163" s="1">
         <v>5</v>
@@ -6758,8 +6762,8 @@
       <c r="D164" t="s">
         <v>499</v>
       </c>
-      <c r="E164" s="1">
-        <v>12000</v>
+      <c r="E164" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F164" s="1">
         <v>5</v>
@@ -6787,8 +6791,8 @@
       <c r="D165" t="s">
         <v>502</v>
       </c>
-      <c r="E165" s="1">
-        <v>12000</v>
+      <c r="E165" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F165" s="1">
         <v>5</v>
@@ -6816,8 +6820,8 @@
       <c r="D166" t="s">
         <v>505</v>
       </c>
-      <c r="E166" s="1">
-        <v>12000</v>
+      <c r="E166" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="F166" s="1">
         <v>5</v>
